--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
@@ -31,7 +31,7 @@
     <t>A*</t>
   </si>
   <si>
-    <t>JPS-BDS-GL-BRC-PPO</t>
+    <t>JPS-GL-BRC-PPO</t>
   </si>
   <si>
     <t>Map_1</t>
@@ -552,7 +552,7 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -580,7 +580,7 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -608,7 +608,7 @@
         <v>64</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -636,7 +636,7 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -720,7 +720,7 @@
         <v>64</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -748,7 +748,7 @@
         <v>128</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -776,7 +776,7 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="s">
         <v>8</v>
@@ -860,7 +860,7 @@
         <v>128</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
         <v>8</v>
@@ -888,7 +888,7 @@
         <v>16</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -944,7 +944,7 @@
         <v>64</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -972,7 +972,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B0CA30-5A95-47A2-B653-8AB5B9E5B17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="10">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -49,8 +55,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,7 +81,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,14 +104,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -113,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -225,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -400,11 +431,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -414,11 +448,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -428,11 +460,11 @@
       <c r="C2">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -442,11 +474,9 @@
       <c r="C3">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -456,11 +486,9 @@
       <c r="C4">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -470,11 +498,9 @@
       <c r="C5">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -484,11 +510,9 @@
       <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -498,11 +522,9 @@
       <c r="C7">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -512,11 +534,9 @@
       <c r="C8">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -526,11 +546,9 @@
       <c r="C9">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -540,11 +558,11 @@
       <c r="C10">
         <v>12</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -554,11 +572,9 @@
       <c r="C11">
         <v>7</v>
       </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -568,11 +584,9 @@
       <c r="C12">
         <v>12</v>
       </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -582,11 +596,9 @@
       <c r="C13">
         <v>9</v>
       </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -596,11 +608,9 @@
       <c r="C14">
         <v>18</v>
       </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -610,11 +620,9 @@
       <c r="C15">
         <v>9</v>
       </c>
-      <c r="D15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -624,11 +632,9 @@
       <c r="C16">
         <v>32</v>
       </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -638,11 +644,9 @@
       <c r="C17">
         <v>9</v>
       </c>
-      <c r="D17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -656,7 +660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -670,7 +674,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -684,7 +688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -698,7 +702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -712,7 +716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -726,7 +730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -740,7 +744,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -754,7 +758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -768,7 +772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -782,7 +786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -796,7 +800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -810,7 +814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -824,7 +828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -838,7 +842,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -852,7 +856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -866,7 +870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -880,7 +884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -894,7 +898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -908,7 +912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -922,7 +926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -936,7 +940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -950,7 +954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -964,7 +968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -979,6 +983,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D9"/>
+    <mergeCell ref="D10:D17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -771,7 +771,7 @@
         <v>16</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
@@ -841,7 +841,7 @@
         <v>32</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -911,7 +911,7 @@
         <v>64</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -981,7 +981,7 @@
         <v>128</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
         <v>9</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
@@ -1401,7 +1401,7 @@
         <v>32</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
@@ -1541,7 +1541,7 @@
         <v>128</v>
       </c>
       <c r="C81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>

--- a/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
+++ b/Excel/Vertical/hasil_gabungan_vertikal_Jumlah Belok.xlsx
@@ -491,7 +491,7 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
@@ -519,7 +519,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
@@ -589,7 +589,7 @@
         <v>64</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
@@ -659,7 +659,7 @@
         <v>128</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
         <v>3</v>
@@ -799,7 +799,7 @@
         <v>32</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -869,7 +869,7 @@
         <v>64</v>
       </c>
       <c r="C33">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>128</v>
       </c>
       <c r="C38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -1149,7 +1149,7 @@
         <v>64</v>
       </c>
       <c r="C53">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>128</v>
       </c>
       <c r="C58">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D58" t="s">
         <v>10</v>
@@ -1359,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="C68">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
@@ -1429,7 +1429,7 @@
         <v>64</v>
       </c>
       <c r="C73">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>128</v>
       </c>
       <c r="C78">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
@@ -1779,7 +1779,7 @@
         <v>128</v>
       </c>
       <c r="C98">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
         <v>12</v>
